--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>06/26 08:48:20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55192.2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>55192.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/26 14:18:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>460000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>55192.2</t>
+          <t>460000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55192.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>55192.2</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06/26 08:48:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>36144.58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 14:18:46</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>55192</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>460000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>55192.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>55192</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.2</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/02 12:31:26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/07 18:23:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/07 18:23:19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>36144</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>119047.62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36144</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.58</t>
+          <t>119047.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/08 14:16:26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>119047</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1000000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119047.62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>119047</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>119047.62</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/08 14:16:26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>119047</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>119047</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.62</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/09 16:13:47</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24096.39</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/09 16:13:47</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>259980</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>29048.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24096</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.39</t>
+          <t>29048.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/10 18:09:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>259980</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>259980</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29048.04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>29048.04</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/10 18:09:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>29048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>29940.12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.04</t>
+          <t>29940.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/15 14:23:24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29940</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29940.12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29940</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>29940.12</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/15 14:23:24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>29940</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>120989</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>13443.22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29940</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.12</t>
+          <t>13443.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/17 10:47:27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>120989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>120989</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13443.22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13443.22</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13355.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/17 18:39:08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>44578.31</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/17 10:47:05</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>120989</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>13443.22</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/17 10:47:27</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>120989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>490989</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>58021.54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>13355.22</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>57933.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/17 18:39:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/17 10:47:27</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>490989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58021.54</t>
+          <t>490989</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>58021.54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>57933.54</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>56933.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/17 18:39:32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/17 10:47:27</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>490989</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>58021.54</t>
+          <t>490989</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>58021.54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>58021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>56933.54</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.54</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,267 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/17 10:47:05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>120989</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>13443.22</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>56933</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>11976.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>490989</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>58021.54</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>58021</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.54</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11976.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/21 16:48:48</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11976.05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11976.05</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/21 16:48:48</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11976</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>26190.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11976</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.05</t>
+          <t>26190.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/22 14:20:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26190</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26190.48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26190</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>26190.48</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/22 16:06:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>32697</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3758.28</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/22 11:02:56</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>26190.48</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/22 14:20:08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>26190</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>252697</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>29948.75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26190</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.48</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3758.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/22 16:12:46</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/22 14:20:08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>26190</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>252697</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29948.75</t>
+          <t>252697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>29948.75</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29948</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3758.75</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/22 11:02:56</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>26190.48</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3758</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26190</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>51996</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5976.55</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>252697</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29948.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>29948</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.75</t>
+          <t>5976.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/24 20:41:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>51996</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>51996</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5976.55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5976</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5976.55</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/24 20:41:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5976</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5976</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.55</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -72,186 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>07/25 11:57:40</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2344.6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2344.6</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2344.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/25 13:04:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20398</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2344.6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20398</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2344.6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2344.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/25 19:32:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>32097</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3689.31</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/25 13:04:40</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2344.6</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>20398</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>52495</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6033.91</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2344.6</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6033.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07/25 19:35:26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6033</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>52495</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6033.91</t>
+          <t>52495</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6033.91</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6033</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6033.91</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/25 13:04:40</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20398</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2344.6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>6033</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7407.41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52495</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6033.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6033</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.91</t>
+          <t>7407.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/31 16:20:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>60000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>60000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7407.41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7407.41</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/31 16:20:29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>40000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>4938.27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7407</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.41</t>
+          <t>4938.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/02 14:59:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>40000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>40000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4938.27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>4938.27</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/02 14:59:07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>83443.5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>10176.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4938</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.27</t>
+          <t>10176.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/03 14:06:46</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>83443.5</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>83443.5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10176.04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10176.04</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.04</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/03 14:06:46</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10176</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10176</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.04</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
+++ b/bills/JXZFSP/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/05 16:20:51</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12345.68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12345.68</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.68</t>
         </is>
       </c>
     </row>
